--- a/public/plantillas/11_PROG_UTILIZACION_VEHICULOS.xlsx
+++ b/public/plantillas/11_PROG_UTILIZACION_VEHICULOS.xlsx
@@ -8,15 +8,15 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/ventura/Desktop/Programacion/recal-hse/public/plantillas/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F8D05C82-5FBF-BB42-9206-F424A57A7E58}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{93AEFAE0-6ECE-3A47-B02A-454D50519387}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="33600" windowHeight="21000" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="3620" yWindow="0" windowWidth="29980" windowHeight="21000" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="MANTENIMIENTO VEHICULOS" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm.Print_Area" localSheetId="0">'MANTENIMIENTO VEHICULOS'!$A$1:$H$8</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">'MANTENIMIENTO VEHICULOS'!$A$1:$H$9</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="0">'MANTENIMIENTO VEHICULOS'!$1:$4</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="17" uniqueCount="17">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="15" uniqueCount="15">
   <si>
     <t>NO.</t>
   </si>
@@ -55,10 +55,6 @@
   </si>
   <si>
     <t>CONTRATISTA: RECAL ESTRUCTURAS</t>
-  </si>
-  <si>
-    <t xml:space="preserve">
-OBSERVACIONES:</t>
   </si>
   <si>
     <t xml:space="preserve">FECHA: </t>
@@ -85,13 +81,10 @@
     <t>NÚMERO ECONOMICO</t>
   </si>
   <si>
-    <t>AUTORIZÓ</t>
+    <t>REVISÓ</t>
   </si>
   <si>
-    <t>OSVALDO JIMENEZ MORALES</t>
-  </si>
-  <si>
-    <t>ANTONIO SATURNO FRANCISCO RAMON</t>
+    <t>OBSERVACIONES:</t>
   </si>
 </sst>
 </file>
@@ -220,7 +213,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="8">
+  <borders count="10">
     <border>
       <left/>
       <right/>
@@ -313,11 +306,31 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="26">
+  <cellXfs count="33">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -350,21 +363,37 @@
     <xf numFmtId="0" fontId="8" fillId="7" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="6" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="6" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="5" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="5" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -391,6 +420,9 @@
     </xf>
     <xf numFmtId="0" fontId="11" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -702,7 +734,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:U984"/>
+  <dimension ref="A1:U985"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="12.5" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="1" max="1" width="9.83203125" customWidth="1"/>
@@ -717,42 +749,42 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:21" ht="60" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A1" s="17" t="s">
-        <v>11</v>
+      <c r="A1" s="23" t="s">
+        <v>10</v>
       </c>
-      <c r="B1" s="17"/>
-      <c r="C1" s="17"/>
-      <c r="D1" s="17"/>
-      <c r="E1" s="17"/>
-      <c r="F1" s="17"/>
-      <c r="G1" s="17"/>
-      <c r="H1" s="17"/>
+      <c r="B1" s="23"/>
+      <c r="C1" s="23"/>
+      <c r="D1" s="23"/>
+      <c r="E1" s="23"/>
+      <c r="F1" s="23"/>
+      <c r="G1" s="23"/>
+      <c r="H1" s="23"/>
     </row>
     <row r="2" spans="1:21" ht="27" x14ac:dyDescent="0.15">
-      <c r="A2" s="23" t="s">
-        <v>8</v>
+      <c r="A2" s="29" t="s">
+        <v>7</v>
       </c>
-      <c r="B2" s="24"/>
-      <c r="C2" s="24"/>
-      <c r="D2" s="25"/>
-      <c r="E2" s="18" t="s">
-        <v>6</v>
+      <c r="B2" s="30"/>
+      <c r="C2" s="30"/>
+      <c r="D2" s="31"/>
+      <c r="E2" s="24" t="s">
+        <v>5</v>
       </c>
-      <c r="F2" s="19"/>
-      <c r="G2" s="19"/>
-      <c r="H2" s="19"/>
+      <c r="F2" s="25"/>
+      <c r="G2" s="25"/>
+      <c r="H2" s="25"/>
     </row>
     <row r="3" spans="1:21" ht="49" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A3" s="18" t="s">
+      <c r="A3" s="24" t="s">
         <v>4</v>
       </c>
-      <c r="B3" s="19"/>
-      <c r="C3" s="19"/>
-      <c r="D3" s="22"/>
-      <c r="E3" s="20"/>
-      <c r="F3" s="21"/>
-      <c r="G3" s="21"/>
-      <c r="H3" s="21"/>
+      <c r="B3" s="25"/>
+      <c r="C3" s="25"/>
+      <c r="D3" s="28"/>
+      <c r="E3" s="26"/>
+      <c r="F3" s="27"/>
+      <c r="G3" s="27"/>
+      <c r="H3" s="27"/>
     </row>
     <row r="4" spans="1:21" ht="50" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A4" s="3" t="s">
@@ -768,16 +800,16 @@
         <v>3</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="F4" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="G4" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="G4" s="5" t="s">
-        <v>10</v>
-      </c>
       <c r="H4" s="8" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="5" spans="1:21" ht="157" customHeight="1" x14ac:dyDescent="0.15">
@@ -790,62 +822,67 @@
       <c r="G5" s="7"/>
       <c r="H5" s="6"/>
     </row>
-    <row r="6" spans="1:21" ht="69" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A6" s="16" t="s">
-        <v>5</v>
-      </c>
-      <c r="B6" s="16"/>
-      <c r="C6" s="16"/>
-      <c r="D6" s="16"/>
-      <c r="E6" s="16"/>
-      <c r="F6" s="16"/>
-      <c r="G6" s="16"/>
-      <c r="H6" s="16"/>
+    <row r="6" spans="1:21" ht="157" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A6" s="9"/>
+      <c r="B6" s="10"/>
+      <c r="C6" s="9"/>
+      <c r="D6" s="11"/>
+      <c r="E6" s="9"/>
+      <c r="F6" s="7"/>
+      <c r="G6" s="7"/>
+      <c r="H6" s="6"/>
     </row>
-    <row r="7" spans="1:21" ht="13.5" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A7" s="12" t="s">
-        <v>12</v>
+    <row r="7" spans="1:21" ht="69" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A7" s="32" t="s">
+        <v>14</v>
       </c>
       <c r="B7" s="13"/>
       <c r="C7" s="13"/>
       <c r="D7" s="13"/>
-      <c r="E7" s="12" t="s">
-        <v>14</v>
-      </c>
+      <c r="E7" s="13"/>
       <c r="F7" s="13"/>
       <c r="G7" s="13"/>
-      <c r="H7" s="13"/>
-      <c r="J7" s="2"/>
-      <c r="K7" s="2"/>
-      <c r="L7" s="2"/>
-      <c r="M7" s="2"/>
-      <c r="N7" s="2"/>
-      <c r="O7" s="2"/>
-      <c r="P7" s="2"/>
-      <c r="Q7" s="2"/>
-      <c r="R7" s="2"/>
-      <c r="S7" s="2"/>
-      <c r="T7" s="2"/>
-      <c r="U7" s="2"/>
+      <c r="H7" s="14"/>
     </row>
-    <row r="8" spans="1:21" ht="81" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="14" t="s">
-        <v>15</v>
+    <row r="8" spans="1:21" ht="13.5" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A8" s="15"/>
+      <c r="B8" s="16"/>
+      <c r="C8" s="17" t="s">
+        <v>11</v>
       </c>
-      <c r="B8" s="15"/>
-      <c r="C8" s="15"/>
-      <c r="D8" s="15"/>
-      <c r="E8" s="14" t="s">
-        <v>16</v>
+      <c r="D8" s="16"/>
+      <c r="E8" s="15"/>
+      <c r="F8" s="18" t="s">
+        <v>13</v>
       </c>
-      <c r="F8" s="15"/>
-      <c r="G8" s="15"/>
-      <c r="H8" s="15"/>
+      <c r="G8" s="16"/>
+      <c r="H8" s="16"/>
+      <c r="J8" s="2"/>
+      <c r="K8" s="2"/>
+      <c r="L8" s="2"/>
+      <c r="M8" s="2"/>
+      <c r="N8" s="2"/>
+      <c r="O8" s="2"/>
+      <c r="P8" s="2"/>
+      <c r="Q8" s="2"/>
+      <c r="R8" s="2"/>
+      <c r="S8" s="2"/>
+      <c r="T8" s="2"/>
+      <c r="U8" s="2"/>
     </row>
-    <row r="9" spans="1:21" ht="30.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="10" spans="1:21" ht="52.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="11" spans="1:21" ht="8.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="12" spans="1:21" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="9" spans="1:21" ht="81" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A9" s="19"/>
+      <c r="B9" s="20"/>
+      <c r="C9" s="12"/>
+      <c r="D9" s="21"/>
+      <c r="E9" s="19"/>
+      <c r="F9" s="22"/>
+      <c r="G9" s="20"/>
+      <c r="H9" s="20"/>
+    </row>
+    <row r="10" spans="1:21" ht="30.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="11" spans="1:21" ht="52.5" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="12" spans="1:21" ht="8.25" customHeight="1" x14ac:dyDescent="0.15"/>
     <row r="13" spans="1:21" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
     <row r="14" spans="1:21" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
     <row r="15" spans="1:21" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
@@ -1818,18 +1855,14 @@
     <row r="982" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
     <row r="983" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
     <row r="984" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="985" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
   </sheetData>
-  <mergeCells count="10">
+  <mergeCells count="5">
     <mergeCell ref="A1:H1"/>
     <mergeCell ref="E2:H2"/>
     <mergeCell ref="E3:H3"/>
     <mergeCell ref="A3:D3"/>
     <mergeCell ref="A2:D2"/>
-    <mergeCell ref="A7:D7"/>
-    <mergeCell ref="E7:H7"/>
-    <mergeCell ref="A8:D8"/>
-    <mergeCell ref="E8:H8"/>
-    <mergeCell ref="A6:H6"/>
   </mergeCells>
   <phoneticPr fontId="6" type="noConversion"/>
   <printOptions horizontalCentered="1" verticalCentered="1"/>

--- a/public/plantillas/11_PROG_UTILIZACION_VEHICULOS.xlsx
+++ b/public/plantillas/11_PROG_UTILIZACION_VEHICULOS.xlsx
@@ -8,15 +8,15 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/ventura/Desktop/Programacion/recal-hse/public/plantillas/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{93AEFAE0-6ECE-3A47-B02A-454D50519387}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{62DCEC7B-211C-C244-B6A1-8387D77DA7CF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3620" yWindow="0" windowWidth="29980" windowHeight="21000" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="33600" windowHeight="21000" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="MANTENIMIENTO VEHICULOS" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm.Print_Area" localSheetId="0">'MANTENIMIENTO VEHICULOS'!$A$1:$H$9</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">'MANTENIMIENTO VEHICULOS'!$A$1:$H$8</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="0">'MANTENIMIENTO VEHICULOS'!$1:$4</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
@@ -394,6 +394,9 @@
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="5" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -420,9 +423,6 @@
     </xf>
     <xf numFmtId="0" fontId="11" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -734,7 +734,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:U985"/>
+  <dimension ref="A1:U984"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="12.5" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="1" max="1" width="9.83203125" customWidth="1"/>
@@ -749,42 +749,42 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:21" ht="60" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A1" s="23" t="s">
+      <c r="A1" s="24" t="s">
         <v>10</v>
       </c>
-      <c r="B1" s="23"/>
-      <c r="C1" s="23"/>
-      <c r="D1" s="23"/>
-      <c r="E1" s="23"/>
-      <c r="F1" s="23"/>
-      <c r="G1" s="23"/>
-      <c r="H1" s="23"/>
+      <c r="B1" s="24"/>
+      <c r="C1" s="24"/>
+      <c r="D1" s="24"/>
+      <c r="E1" s="24"/>
+      <c r="F1" s="24"/>
+      <c r="G1" s="24"/>
+      <c r="H1" s="24"/>
     </row>
     <row r="2" spans="1:21" ht="27" x14ac:dyDescent="0.15">
-      <c r="A2" s="29" t="s">
+      <c r="A2" s="30" t="s">
         <v>7</v>
       </c>
-      <c r="B2" s="30"/>
-      <c r="C2" s="30"/>
-      <c r="D2" s="31"/>
-      <c r="E2" s="24" t="s">
+      <c r="B2" s="31"/>
+      <c r="C2" s="31"/>
+      <c r="D2" s="32"/>
+      <c r="E2" s="25" t="s">
         <v>5</v>
       </c>
-      <c r="F2" s="25"/>
-      <c r="G2" s="25"/>
-      <c r="H2" s="25"/>
+      <c r="F2" s="26"/>
+      <c r="G2" s="26"/>
+      <c r="H2" s="26"/>
     </row>
     <row r="3" spans="1:21" ht="49" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A3" s="24" t="s">
+      <c r="A3" s="25" t="s">
         <v>4</v>
       </c>
-      <c r="B3" s="25"/>
-      <c r="C3" s="25"/>
-      <c r="D3" s="28"/>
-      <c r="E3" s="26"/>
-      <c r="F3" s="27"/>
-      <c r="G3" s="27"/>
-      <c r="H3" s="27"/>
+      <c r="B3" s="26"/>
+      <c r="C3" s="26"/>
+      <c r="D3" s="29"/>
+      <c r="E3" s="27"/>
+      <c r="F3" s="28"/>
+      <c r="G3" s="28"/>
+      <c r="H3" s="28"/>
     </row>
     <row r="4" spans="1:21" ht="50" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A4" s="3" t="s">
@@ -822,67 +822,58 @@
       <c r="G5" s="7"/>
       <c r="H5" s="6"/>
     </row>
-    <row r="6" spans="1:21" ht="157" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A6" s="9"/>
-      <c r="B6" s="10"/>
-      <c r="C6" s="9"/>
-      <c r="D6" s="11"/>
-      <c r="E6" s="9"/>
-      <c r="F6" s="7"/>
-      <c r="G6" s="7"/>
-      <c r="H6" s="6"/>
-    </row>
-    <row r="7" spans="1:21" ht="69" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A7" s="32" t="s">
+    <row r="6" spans="1:21" ht="69" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A6" s="23" t="s">
         <v>14</v>
       </c>
-      <c r="B7" s="13"/>
-      <c r="C7" s="13"/>
-      <c r="D7" s="13"/>
-      <c r="E7" s="13"/>
-      <c r="F7" s="13"/>
-      <c r="G7" s="13"/>
-      <c r="H7" s="14"/>
+      <c r="B6" s="13"/>
+      <c r="C6" s="13"/>
+      <c r="D6" s="13"/>
+      <c r="E6" s="13"/>
+      <c r="F6" s="13"/>
+      <c r="G6" s="13"/>
+      <c r="H6" s="14"/>
     </row>
-    <row r="8" spans="1:21" ht="13.5" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A8" s="15"/>
-      <c r="B8" s="16"/>
-      <c r="C8" s="17" t="s">
+    <row r="7" spans="1:21" ht="13.5" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A7" s="15"/>
+      <c r="B7" s="16"/>
+      <c r="C7" s="17" t="s">
         <v>11</v>
       </c>
-      <c r="D8" s="16"/>
-      <c r="E8" s="15"/>
-      <c r="F8" s="18" t="s">
+      <c r="D7" s="16"/>
+      <c r="E7" s="15"/>
+      <c r="F7" s="18" t="s">
         <v>13</v>
       </c>
-      <c r="G8" s="16"/>
-      <c r="H8" s="16"/>
-      <c r="J8" s="2"/>
-      <c r="K8" s="2"/>
-      <c r="L8" s="2"/>
-      <c r="M8" s="2"/>
-      <c r="N8" s="2"/>
-      <c r="O8" s="2"/>
-      <c r="P8" s="2"/>
-      <c r="Q8" s="2"/>
-      <c r="R8" s="2"/>
-      <c r="S8" s="2"/>
-      <c r="T8" s="2"/>
-      <c r="U8" s="2"/>
+      <c r="G7" s="16"/>
+      <c r="H7" s="16"/>
+      <c r="J7" s="2"/>
+      <c r="K7" s="2"/>
+      <c r="L7" s="2"/>
+      <c r="M7" s="2"/>
+      <c r="N7" s="2"/>
+      <c r="O7" s="2"/>
+      <c r="P7" s="2"/>
+      <c r="Q7" s="2"/>
+      <c r="R7" s="2"/>
+      <c r="S7" s="2"/>
+      <c r="T7" s="2"/>
+      <c r="U7" s="2"/>
     </row>
-    <row r="9" spans="1:21" ht="81" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="19"/>
-      <c r="B9" s="20"/>
-      <c r="C9" s="12"/>
-      <c r="D9" s="21"/>
-      <c r="E9" s="19"/>
-      <c r="F9" s="22"/>
-      <c r="G9" s="20"/>
-      <c r="H9" s="20"/>
+    <row r="8" spans="1:21" ht="81" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8" s="19"/>
+      <c r="B8" s="20"/>
+      <c r="C8" s="12"/>
+      <c r="D8" s="21"/>
+      <c r="E8" s="19"/>
+      <c r="F8" s="22"/>
+      <c r="G8" s="20"/>
+      <c r="H8" s="20"/>
     </row>
-    <row r="10" spans="1:21" ht="30.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="11" spans="1:21" ht="52.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="12" spans="1:21" ht="8.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="9" spans="1:21" ht="30.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="10" spans="1:21" ht="52.5" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="11" spans="1:21" ht="8.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="12" spans="1:21" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
     <row r="13" spans="1:21" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
     <row r="14" spans="1:21" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
     <row r="15" spans="1:21" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
@@ -1855,7 +1846,6 @@
     <row r="982" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
     <row r="983" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
     <row r="984" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="985" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
   </sheetData>
   <mergeCells count="5">
     <mergeCell ref="A1:H1"/>
